--- a/data-manipulation-scripts/sheets-cleanup/sheets/KIT TENSOR CORRENTE_.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/KIT TENSOR CORRENTE_.xlsx
@@ -131,7 +131,7 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
@@ -437,7 +437,9 @@
       <c r="C3" s="4">
         <v>1.0</v>
       </c>
-      <c r="D3" s="6"/>
+      <c r="D3" s="6">
+        <v>30.0</v>
+      </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -507,7 +509,9 @@
       <c r="C5" s="7">
         <v>1.0</v>
       </c>
-      <c r="D5" s="5"/>
+      <c r="D5" s="6">
+        <v>30.0</v>
+      </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
@@ -577,7 +581,9 @@
       <c r="C7" s="7">
         <v>1.0</v>
       </c>
-      <c r="D7" s="5"/>
+      <c r="D7" s="6">
+        <v>40.0</v>
+      </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
@@ -611,7 +617,9 @@
       <c r="C8" s="7">
         <v>3.0</v>
       </c>
-      <c r="D8" s="5"/>
+      <c r="D8" s="6">
+        <v>40.0</v>
+      </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
